--- a/新章节编辑/pandas/backup/data/industry_2020_full_summary.xlsx
+++ b/新章节编辑/pandas/backup/data/industry_2020_full_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>公司数</t>
   </si>
@@ -34,9 +34,6 @@
     <t>行业名称</t>
   </si>
   <si>
-    <t>货币金融服务</t>
-  </si>
-  <si>
     <t>房地产业</t>
   </si>
   <si>
@@ -49,10 +46,10 @@
     <t>计算机、通信和其他电子设备制造业</t>
   </si>
   <si>
+    <t>软件和信息技术服务业</t>
+  </si>
+  <si>
     <t>医药制造业</t>
-  </si>
-  <si>
-    <t>软件和信息技术服务业</t>
   </si>
 </sst>
 </file>
@@ -410,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -441,16 +438,16 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>1443.5575</v>
+        <v>1066.245</v>
       </c>
       <c r="D2">
-        <v>5774.23</v>
+        <v>4264.98</v>
       </c>
       <c r="E2">
-        <v>0.2456883319622854</v>
+        <v>0.1633016150759633</v>
       </c>
       <c r="F2">
-        <v>0.919075</v>
+        <v>0.6508437499999999</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -461,16 +458,16 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>1065.49</v>
+        <v>798.8299999999999</v>
       </c>
       <c r="D3">
-        <v>4261.96</v>
+        <v>3195.32</v>
       </c>
       <c r="E3">
-        <v>-0.5265158681132778</v>
+        <v>0.05474140103256352</v>
       </c>
       <c r="F3">
-        <v>0.7023</v>
+        <v>0.62517475</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -481,16 +478,16 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>813.045</v>
+        <v>631.455</v>
       </c>
       <c r="D4">
-        <v>3252.18</v>
+        <v>2525.82</v>
       </c>
       <c r="E4">
-        <v>0.03539331681490884</v>
+        <v>0.04906179501368793</v>
       </c>
       <c r="F4">
-        <v>0.676075</v>
+        <v>0.54248175</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -501,16 +498,16 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>631.455</v>
+        <v>170.3</v>
       </c>
       <c r="D5">
-        <v>2525.82</v>
+        <v>681.1999999999999</v>
       </c>
       <c r="E5">
-        <v>0.04906179501368793</v>
+        <v>0.02622558279206509</v>
       </c>
       <c r="F5">
-        <v>0.5424749999999999</v>
+        <v>0.52363825</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -521,16 +518,16 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>170.3</v>
+        <v>36.9925</v>
       </c>
       <c r="D6">
-        <v>681.1999999999999</v>
+        <v>147.97</v>
       </c>
       <c r="E6">
-        <v>0.02622558279206509</v>
+        <v>0.04232670401929352</v>
       </c>
       <c r="F6">
-        <v>0.523675</v>
+        <v>0.428373</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -538,39 +535,19 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>124.9825</v>
+        <v>25.93333333333334</v>
       </c>
       <c r="D7">
-        <v>499.93</v>
+        <v>77.80000000000001</v>
       </c>
       <c r="E7">
-        <v>0.1034044879410964</v>
+        <v>0.07234211404726087</v>
       </c>
       <c r="F7">
-        <v>0.338025</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>52.405</v>
-      </c>
-      <c r="D8">
-        <v>209.62</v>
-      </c>
-      <c r="E8">
-        <v>0.0237236063928227</v>
-      </c>
-      <c r="F8">
-        <v>0.464825</v>
+        <v>0.3746123333333333</v>
       </c>
     </row>
   </sheetData>
